--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-04-2026.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£20.11</t>
+          <t>£13.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>£23.87</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£53.85</t>
+          <t>£15.08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£26.73</t>
+          <t>£19.34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£46.31</t>
+          <t>£19.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£26.23</t>
+          <t>£25.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£48.46</t>
+          <t>£27.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£36.61</t>
+          <t>£27.62</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£12.57</t>
+          <t>£31.48</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£10.94</t>
+          <t>£34.47</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£94.34</t>
+          <t>£32.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£10.94</t>
+          <t>£49.11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£26.73</t>
+          <t>£41.23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£94.34</t>
+          <t>£54.92</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£64.62</t>
+          <t>£55.57</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>£131.30</t>
+          <t>£1008.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>£863.30</t>
+          <t>£902.08</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>£272.00</t>
+          <t>£1209.7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£53.85</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£71.30</t>
+          <t>£55.57</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£85.42</t>
+          <t>£58.15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£288.57</t>
+          <t>£92.31</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£275.73</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£49.79</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>£274.65</t>
+          <t>£96.25</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>£1930.40</t>
+          <t>£1376.8</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>£2138.67</t>
+          <t>£1653.33</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>£1473.07</t>
+          <t>£1571.2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
